--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$C$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$C$3:$G$26</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="54">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -124,6 +124,66 @@
   </si>
   <si>
     <t>hizo sus trabajos</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>Va mejorando</t>
+  </si>
+  <si>
+    <t>va bien. Va bien</t>
+  </si>
+  <si>
+    <t>BRIZUELA, Lourdes</t>
+  </si>
+  <si>
+    <t>BRIZUELA, Lucas</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>SORIA, Candelaria</t>
+  </si>
+  <si>
+    <t>ARRASCAETA, Benjamín</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>SORIA, Isaac Ezequiel</t>
+  </si>
+  <si>
+    <t>LEAL, Eric Ivan</t>
+  </si>
+  <si>
+    <t>DIAZ, Thiago Ezequiel</t>
+  </si>
+  <si>
+    <t>SINCHICAY, Selena Salomé</t>
+  </si>
+  <si>
+    <t>VILLAFAÑEZ, Ismael David</t>
+  </si>
+  <si>
+    <t>SOSA, Ramiro Benjamín</t>
+  </si>
+  <si>
+    <t>NAVARRO, Octaviano</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Excelente</t>
+  </si>
+  <si>
+    <t>TP CLASES</t>
+  </si>
+  <si>
+    <t>PREMIO</t>
   </si>
 </sst>
 </file>
@@ -465,14 +525,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:H24"/>
+  <dimension ref="B2:H42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" customWidth="1"/>
     <col min="8" max="8" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -685,7 +745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>10</v>
       </c>
@@ -702,7 +762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>12</v>
       </c>
@@ -719,7 +779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>13</v>
       </c>
@@ -733,7 +793,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -750,7 +810,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>20</v>
       </c>
@@ -767,7 +827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>0</v>
       </c>
@@ -787,7 +847,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>32</v>
       </c>
@@ -804,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>18</v>
       </c>
@@ -815,8 +875,188 @@
         <v>33</v>
       </c>
     </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C3:G3"/>
+  <autoFilter ref="C3:G26"/>
   <mergeCells count="1">
     <mergeCell ref="C2:G2"/>
   </mergeCells>

--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$C$3:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$42</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="56">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -150,9 +150,6 @@
     <t>ARRASCAETA, Benjamín</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>SORIA, Isaac Ezequiel</t>
   </si>
   <si>
@@ -184,13 +181,22 @@
   </si>
   <si>
     <t>PREMIO</t>
+  </si>
+  <si>
+    <t>SITUACIÓN</t>
+  </si>
+  <si>
+    <t>NO PRESENTA</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,8 +212,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,6 +240,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -239,12 +259,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,27 +546,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H42"/>
+  <dimension ref="B2:H46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -560,7 +586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -574,7 +600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -588,7 +614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -602,7 +628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -616,7 +642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -630,7 +656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -644,7 +670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>15</v>
       </c>
@@ -658,7 +684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -672,7 +698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>20</v>
       </c>
@@ -686,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>21</v>
       </c>
@@ -700,7 +726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>22</v>
       </c>
@@ -714,7 +740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>23</v>
       </c>
@@ -728,7 +754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>24</v>
       </c>
@@ -919,13 +945,13 @@
         <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -951,7 +977,7 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>41</v>
@@ -967,26 +993,26 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
@@ -994,15 +1020,15 @@
         <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
@@ -1010,12 +1036,12 @@
         <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
@@ -1024,15 +1050,15 @@
         <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -1041,24 +1067,68 @@
         <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C3:G26"/>
+  <autoFilter ref="B3:G42"/>
   <mergeCells count="1">
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$54</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="62">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -190,6 +190,24 @@
   </si>
   <si>
     <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>17.06.2026</t>
+  </si>
+  <si>
+    <t>EVALUACION</t>
+  </si>
+  <si>
+    <t>Ulla Cabral, Jeremías</t>
+  </si>
+  <si>
+    <t>SORIA, Lourdes Candelaria</t>
+  </si>
+  <si>
+    <t>TANQUÍA, Alexander</t>
+  </si>
+  <si>
+    <t>APROBADO</t>
   </si>
 </sst>
 </file>
@@ -221,7 +239,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,6 +264,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -259,13 +283,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H46"/>
+  <dimension ref="B2:H70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -559,17 +584,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1125,8 +1150,314 @@
         <v>55</v>
       </c>
     </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" t="s">
+        <v>56</v>
+      </c>
+      <c r="E54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E55" t="s">
+        <v>57</v>
+      </c>
+      <c r="G55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>56</v>
+      </c>
+      <c r="E61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>56</v>
+      </c>
+      <c r="E67" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B3:G42"/>
+  <autoFilter ref="B3:G54"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>

--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="65">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -208,6 +208,15 @@
   </si>
   <si>
     <t>APROBADO</t>
+  </si>
+  <si>
+    <t>24.06.2026</t>
+  </si>
+  <si>
+    <t>AUSENTE</t>
+  </si>
+  <si>
+    <t>PRESENTE</t>
   </si>
 </sst>
 </file>
@@ -283,14 +292,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H70"/>
+  <dimension ref="B2:H94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -584,14 +594,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1360,7 +1370,7 @@
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D63" t="s">
@@ -1381,7 +1391,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>12</v>
       </c>
@@ -1395,7 +1405,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>44</v>
       </c>
@@ -1406,8 +1416,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="4" t="s">
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C67" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D67" t="s">
@@ -1417,8 +1427,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C68" s="4" t="s">
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C68" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
@@ -1428,7 +1438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>8</v>
       </c>
@@ -1442,7 +1452,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>22</v>
       </c>
@@ -1453,6 +1463,385 @@
         <v>57</v>
       </c>
       <c r="G70" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>58</v>
+      </c>
+      <c r="D71" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C74" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C75" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>46</v>
+      </c>
+      <c r="D76" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" t="s">
+        <v>62</v>
+      </c>
+      <c r="E79" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" t="s">
+        <v>64</v>
+      </c>
+      <c r="H79" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" t="s">
+        <v>64</v>
+      </c>
+      <c r="H80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" t="s">
+        <v>57</v>
+      </c>
+      <c r="G81" t="s">
+        <v>64</v>
+      </c>
+      <c r="H81" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" t="s">
+        <v>57</v>
+      </c>
+      <c r="G82" t="s">
+        <v>64</v>
+      </c>
+      <c r="H82" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" t="s">
+        <v>62</v>
+      </c>
+      <c r="E83" t="s">
+        <v>57</v>
+      </c>
+      <c r="G83" t="s">
+        <v>64</v>
+      </c>
+      <c r="H83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E84" t="s">
+        <v>57</v>
+      </c>
+      <c r="G84" t="s">
+        <v>64</v>
+      </c>
+      <c r="H84" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s">
+        <v>62</v>
+      </c>
+      <c r="E85" t="s">
+        <v>57</v>
+      </c>
+      <c r="G85" t="s">
+        <v>64</v>
+      </c>
+      <c r="H85" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C86" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>62</v>
+      </c>
+      <c r="E87" t="s">
+        <v>57</v>
+      </c>
+      <c r="G87" t="s">
+        <v>64</v>
+      </c>
+      <c r="H87" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" t="s">
+        <v>62</v>
+      </c>
+      <c r="E88" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>62</v>
+      </c>
+      <c r="E89" t="s">
+        <v>57</v>
+      </c>
+      <c r="G89" t="s">
+        <v>64</v>
+      </c>
+      <c r="H89" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" t="s">
+        <v>62</v>
+      </c>
+      <c r="E90" t="s">
+        <v>57</v>
+      </c>
+      <c r="G90" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" t="s">
+        <v>62</v>
+      </c>
+      <c r="E91" t="s">
+        <v>57</v>
+      </c>
+      <c r="G91" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>62</v>
+      </c>
+      <c r="E92" t="s">
+        <v>57</v>
+      </c>
+      <c r="G92" t="s">
+        <v>64</v>
+      </c>
+      <c r="H92" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
+        <v>62</v>
+      </c>
+      <c r="E93" t="s">
+        <v>57</v>
+      </c>
+      <c r="G93" t="s">
+        <v>64</v>
+      </c>
+      <c r="H93" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" t="s">
+        <v>57</v>
+      </c>
+      <c r="G94" t="s">
+        <v>64</v>
+      </c>
+      <c r="H94" t="s">
         <v>61</v>
       </c>
     </row>

--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="69">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -217,6 +217,18 @@
   </si>
   <si>
     <t>PRESENTE</t>
+  </si>
+  <si>
+    <t>01.07.2026</t>
+  </si>
+  <si>
+    <t>RECUPERATORIO</t>
+  </si>
+  <si>
+    <t>RESULTADO</t>
+  </si>
+  <si>
+    <t>EL SOBRA</t>
   </si>
 </sst>
 </file>
@@ -297,10 +309,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H94"/>
+  <dimension ref="B2:H103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -594,14 +606,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -620,6 +633,9 @@
       <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
@@ -1509,32 +1525,32 @@
       </c>
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5" t="s">
+      <c r="D74" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5" t="s">
+      <c r="D75" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1553,17 +1569,17 @@
       </c>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5" t="s">
+      <c r="D77" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1704,17 +1720,17 @@
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5" t="s">
+      <c r="D86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1845,10 +1861,163 @@
         <v>61</v>
       </c>
     </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" t="s">
+        <v>38</v>
+      </c>
+      <c r="D95" t="s">
+        <v>65</v>
+      </c>
+      <c r="E95" t="s">
+        <v>66</v>
+      </c>
+      <c r="G95" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>65</v>
+      </c>
+      <c r="E96" t="s">
+        <v>66</v>
+      </c>
+      <c r="G96" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>39</v>
+      </c>
+      <c r="C97" t="s">
+        <v>59</v>
+      </c>
+      <c r="D97" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" t="s">
+        <v>66</v>
+      </c>
+      <c r="G97" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" t="s">
+        <v>58</v>
+      </c>
+      <c r="D98" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" t="s">
+        <v>66</v>
+      </c>
+      <c r="G98" t="s">
+        <v>64</v>
+      </c>
+      <c r="H98" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>39</v>
+      </c>
+      <c r="C99" t="s">
+        <v>48</v>
+      </c>
+      <c r="D99" t="s">
+        <v>65</v>
+      </c>
+      <c r="E99" t="s">
+        <v>66</v>
+      </c>
+      <c r="G99" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" t="s">
+        <v>43</v>
+      </c>
+      <c r="D100" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" t="s">
+        <v>66</v>
+      </c>
+      <c r="G100" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>39</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101" t="s">
+        <v>66</v>
+      </c>
+      <c r="G101" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C102" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" t="s">
+        <v>66</v>
+      </c>
+      <c r="G102" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D103" t="s">
+        <v>65</v>
+      </c>
+      <c r="E103" t="s">
+        <v>66</v>
+      </c>
+      <c r="G103" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B3:G54"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2642EE36-4327-41F5-B988-C9E464367F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$H$94</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="67">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -217,12 +219,18 @@
   </si>
   <si>
     <t>PRESENTE</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>1er. CUATRIMESTRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -248,7 +256,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +287,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -292,15 +306,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +597,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B2:H94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -594,14 +612,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -620,8 +639,11 @@
       <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -635,7 +657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -649,7 +671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -663,7 +685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -677,7 +699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -691,7 +713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -705,7 +727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>15</v>
       </c>
@@ -719,7 +741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -733,7 +755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>20</v>
       </c>
@@ -747,7 +769,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>21</v>
       </c>
@@ -761,7 +783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>22</v>
       </c>
@@ -775,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>23</v>
       </c>
@@ -789,7 +811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>24</v>
       </c>
@@ -806,7 +828,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>10</v>
       </c>
@@ -823,7 +845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>12</v>
       </c>
@@ -840,7 +862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>13</v>
       </c>
@@ -854,7 +876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -871,7 +893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>20</v>
       </c>
@@ -888,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>0</v>
       </c>
@@ -908,7 +930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>32</v>
       </c>
@@ -925,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>18</v>
       </c>
@@ -936,7 +958,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>9</v>
       </c>
@@ -947,7 +969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>18</v>
       </c>
@@ -961,7 +983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>24</v>
       </c>
@@ -975,7 +997,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>39</v>
       </c>
@@ -989,7 +1011,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>39</v>
       </c>
@@ -997,7 +1019,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>39</v>
       </c>
@@ -1005,12 +1027,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>54</v>
       </c>
@@ -1018,7 +1040,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>39</v>
       </c>
@@ -1026,7 +1048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>54</v>
       </c>
@@ -1034,7 +1056,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>54</v>
       </c>
@@ -1042,7 +1064,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>54</v>
       </c>
@@ -1050,7 +1072,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>39</v>
       </c>
@@ -1058,7 +1080,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>54</v>
       </c>
@@ -1066,7 +1088,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>39</v>
       </c>
@@ -1074,7 +1096,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>52</v>
       </c>
@@ -1091,7 +1113,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>52</v>
       </c>
@@ -1108,7 +1130,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>52</v>
       </c>
@@ -1116,7 +1138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>52</v>
       </c>
@@ -1127,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>52</v>
       </c>
@@ -1138,7 +1160,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>52</v>
       </c>
@@ -1149,7 +1171,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>52</v>
       </c>
@@ -1160,7 +1182,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>39</v>
       </c>
@@ -1174,7 +1196,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>39</v>
       </c>
@@ -1188,7 +1210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>39</v>
       </c>
@@ -1202,7 +1224,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>39</v>
       </c>
@@ -1216,7 +1238,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>39</v>
       </c>
@@ -1230,7 +1252,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>39</v>
       </c>
@@ -1244,7 +1266,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>39</v>
       </c>
@@ -1258,7 +1280,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>39</v>
       </c>
@@ -1272,7 +1294,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>23</v>
       </c>
@@ -1285,8 +1307,11 @@
       <c r="G55" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>9</v>
       </c>
@@ -1297,7 +1322,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>20</v>
       </c>
@@ -1308,7 +1333,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>32</v>
       </c>
@@ -1319,7 +1344,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>18</v>
       </c>
@@ -1330,7 +1355,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>0</v>
       </c>
@@ -1343,8 +1368,11 @@
       <c r="G60" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H60" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>10</v>
       </c>
@@ -1357,8 +1385,11 @@
       <c r="G61" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>60</v>
       </c>
@@ -1369,7 +1400,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="3" t="s">
         <v>24</v>
       </c>
@@ -1380,7 +1411,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>41</v>
       </c>
@@ -1404,8 +1435,11 @@
       <c r="G65" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>44</v>
       </c>
@@ -1416,7 +1450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C67" s="3" t="s">
         <v>47</v>
       </c>
@@ -1427,7 +1461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C68" s="3" t="s">
         <v>13</v>
       </c>
@@ -1451,8 +1485,11 @@
       <c r="G69" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="H69" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>22</v>
       </c>
@@ -1466,7 +1503,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>58</v>
       </c>
@@ -1480,7 +1517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
         <v>38</v>
       </c>
@@ -1494,7 +1531,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
         <v>37</v>
       </c>
@@ -1508,37 +1545,37 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C74" s="5" t="s">
+    <row r="74" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5" t="s">
+      <c r="D74" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C75" s="5" t="s">
+    <row r="75" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5" t="s">
+      <c r="D75" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>46</v>
       </c>
@@ -1552,22 +1589,22 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C77" s="5" t="s">
+    <row r="77" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5" t="s">
+      <c r="D77" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>42</v>
       </c>
@@ -1703,18 +1740,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="5" t="s">
+    <row r="86" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F86" s="5"/>
-      <c r="G86" s="5" t="s">
+      <c r="D86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1735,7 +1772,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>41</v>
       </c>
@@ -1766,7 +1803,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>44</v>
       </c>
@@ -1780,7 +1817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>47</v>
       </c>
@@ -1846,11 +1883,99 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:G54"/>
+  <autoFilter ref="B3:H94" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="APROBADO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5F4DD5-B0DF-46E5-B2DC-F10760DCBAE9}">
+  <dimension ref="C2:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:C15">
+    <sortCondition ref="C3:C15"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller1_2026/Taller01_2026_ISGM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$G$103</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="68">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -144,9 +144,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>SORIA, Candelaria</t>
-  </si>
-  <si>
     <t>ARRASCAETA, Benjamín</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
     <t>SITUACIÓN</t>
   </si>
   <si>
-    <t>NO PRESENTA</t>
-  </si>
-  <si>
     <t>12.06.2026</t>
   </si>
   <si>
@@ -228,7 +222,10 @@
     <t>RESULTADO</t>
   </si>
   <si>
-    <t>EL SOBRA</t>
+    <t>DESAPROBADO</t>
+  </si>
+  <si>
+    <t>Registrada</t>
   </si>
 </sst>
 </file>
@@ -593,7 +590,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H103"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="B2:I103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -605,7 +603,7 @@
     <col min="8" max="8" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>14</v>
       </c>
@@ -616,9 +614,9 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -634,10 +632,13 @@
         <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -651,7 +652,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -665,7 +669,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -679,7 +686,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -693,7 +703,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -707,7 +720,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -721,7 +737,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
@@ -734,8 +753,14 @@
       <c r="G10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -749,7 +774,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
@@ -763,7 +791,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
@@ -777,7 +808,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
@@ -791,7 +825,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
       <c r="C15" t="s">
         <v>23</v>
       </c>
@@ -805,7 +842,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
@@ -822,7 +862,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
@@ -839,7 +882,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
@@ -856,7 +902,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
@@ -870,7 +919,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -887,7 +939,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
       <c r="C21" t="s">
         <v>20</v>
       </c>
@@ -904,7 +959,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
       <c r="C22" t="s">
         <v>0</v>
       </c>
@@ -924,7 +982,10 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
       <c r="C23" t="s">
         <v>32</v>
       </c>
@@ -941,7 +1002,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
@@ -952,7 +1016,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
@@ -963,7 +1030,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
@@ -977,7 +1047,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
@@ -991,108 +1064,129 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
       <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" t="s">
+    <row r="36" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" t="s">
+    <row r="37" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" t="s">
+    <row r="38" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" t="s">
+    <row r="39" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
@@ -1101,15 +1195,15 @@
         <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C41" t="s">
         <v>23</v>
@@ -1118,904 +1212,1102 @@
         <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="G44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
         <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
         <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
+        <v>55</v>
+      </c>
+      <c r="I49" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I50" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
       <c r="C55" t="s">
         <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
       <c r="C56" t="s">
         <v>9</v>
       </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
       <c r="C58" t="s">
         <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
       <c r="C60" t="s">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
       <c r="C61" t="s">
         <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
       <c r="C64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="3:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>67</v>
+      </c>
       <c r="C65" t="s">
         <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>67</v>
+      </c>
       <c r="C67" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
       <c r="C70" t="s">
         <v>22</v>
       </c>
       <c r="D70" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" t="s">
+        <v>55</v>
+      </c>
+      <c r="G70" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
         <v>56</v>
       </c>
-      <c r="E70" t="s">
-        <v>57</v>
-      </c>
-      <c r="G70" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
-        <v>58</v>
-      </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>67</v>
+      </c>
       <c r="C72" t="s">
         <v>38</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G72" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="I72" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>67</v>
+      </c>
       <c r="C73" t="s">
         <v>37</v>
       </c>
       <c r="D73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E73" t="s">
+        <v>55</v>
+      </c>
+      <c r="G73" t="s">
+        <v>62</v>
+      </c>
+      <c r="I73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G73" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C74" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="D74" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>67</v>
+      </c>
       <c r="C75" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G76" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>67</v>
+      </c>
       <c r="C77" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>67</v>
+      </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G78" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="79" spans="3:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="I78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>67</v>
+      </c>
       <c r="C79" t="s">
         <v>23</v>
       </c>
       <c r="D79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E79" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G79" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H79" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="3:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>67</v>
+      </c>
       <c r="C80" t="s">
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H80" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>67</v>
+      </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G81" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H81" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>67</v>
+      </c>
       <c r="C82" t="s">
         <v>32</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G82" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H82" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C83" t="s">
         <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G83" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H83" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>67</v>
+      </c>
       <c r="C84" t="s">
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E84" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G84" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H84" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>67</v>
+      </c>
       <c r="C85" t="s">
         <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G85" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H85" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>67</v>
+      </c>
       <c r="C86" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="E86" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>67</v>
+      </c>
       <c r="C87" t="s">
         <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G87" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H87" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>67</v>
+      </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D88" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E88" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G88" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>67</v>
+      </c>
       <c r="C89" t="s">
         <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E89" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G89" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H89" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E90" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G90" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>67</v>
+      </c>
       <c r="C91" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E91" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G91" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>67</v>
+      </c>
       <c r="C92" t="s">
         <v>13</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E92" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G92" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H92" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>67</v>
+      </c>
       <c r="C93" t="s">
         <v>8</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E93" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G93" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H93" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>67</v>
+      </c>
       <c r="C94" t="s">
         <v>22</v>
       </c>
       <c r="D94" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G94" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H94" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C95" t="s">
         <v>38</v>
       </c>
       <c r="D95" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E95" t="s">
+        <v>64</v>
+      </c>
+      <c r="G95" t="s">
+        <v>62</v>
+      </c>
+      <c r="H95" t="s">
         <v>66</v>
       </c>
-      <c r="G95" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I95" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C96" t="s">
         <v>37</v>
       </c>
       <c r="D96" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E96" t="s">
+        <v>64</v>
+      </c>
+      <c r="G96" t="s">
+        <v>62</v>
+      </c>
+      <c r="H96" t="s">
         <v>66</v>
       </c>
-      <c r="G96" t="s">
+      <c r="I96" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="G97" t="s">
+        <v>62</v>
+      </c>
+      <c r="H97" t="s">
+        <v>66</v>
+      </c>
+      <c r="I97" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" t="s">
+        <v>56</v>
+      </c>
+      <c r="D98" t="s">
+        <v>63</v>
+      </c>
+      <c r="E98" t="s">
+        <v>64</v>
+      </c>
+      <c r="G98" t="s">
+        <v>62</v>
+      </c>
+      <c r="H98" t="s">
         <v>59</v>
       </c>
-      <c r="D97" t="s">
-        <v>65</v>
-      </c>
-      <c r="E97" t="s">
+    </row>
+    <row r="99" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" t="s">
+        <v>47</v>
+      </c>
+      <c r="D99" t="s">
+        <v>63</v>
+      </c>
+      <c r="E99" t="s">
+        <v>64</v>
+      </c>
+      <c r="G99" t="s">
+        <v>62</v>
+      </c>
+      <c r="H99" t="s">
         <v>66</v>
       </c>
-      <c r="G97" t="s">
+      <c r="I99" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" t="s">
+        <v>63</v>
+      </c>
+      <c r="E100" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>39</v>
-      </c>
-      <c r="C98" t="s">
-        <v>58</v>
-      </c>
-      <c r="D98" t="s">
-        <v>65</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="G100" t="s">
+        <v>62</v>
+      </c>
+      <c r="H100" t="s">
         <v>66</v>
       </c>
-      <c r="G98" t="s">
-        <v>64</v>
-      </c>
-      <c r="H98" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" t="s">
-        <v>48</v>
-      </c>
-      <c r="D99" t="s">
-        <v>65</v>
-      </c>
-      <c r="E99" t="s">
-        <v>66</v>
-      </c>
-      <c r="G99" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
-        <v>68</v>
-      </c>
-      <c r="C100" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" t="s">
-        <v>65</v>
-      </c>
-      <c r="E100" t="s">
-        <v>66</v>
-      </c>
-      <c r="G100" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C101" t="s">
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E101" t="s">
+        <v>64</v>
+      </c>
+      <c r="G101" t="s">
+        <v>62</v>
+      </c>
+      <c r="H101" t="s">
         <v>66</v>
       </c>
-      <c r="G101" t="s">
+      <c r="I101" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" t="s">
+        <v>63</v>
+      </c>
+      <c r="E102" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>39</v>
-      </c>
-      <c r="C102" t="s">
-        <v>46</v>
-      </c>
-      <c r="D102" t="s">
-        <v>65</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
+        <v>62</v>
+      </c>
+      <c r="H102" t="s">
         <v>66</v>
       </c>
-      <c r="G102" t="s">
+    </row>
+    <row r="103" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" t="s">
+        <v>40</v>
+      </c>
+      <c r="D103" t="s">
+        <v>63</v>
+      </c>
+      <c r="E103" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C103" t="s">
-        <v>41</v>
-      </c>
-      <c r="D103" t="s">
-        <v>65</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
+        <v>62</v>
+      </c>
+      <c r="H103" t="s">
         <v>66</v>
       </c>
-      <c r="G103" t="s">
-        <v>64</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:G54"/>
+  <autoFilter ref="B3:G103">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="VERON NIEVA, Maximo Joaquin"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
